--- a/datasets/validacao.xlsx
+++ b/datasets/validacao.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,32 +439,112 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>x4</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Y_T1</t>
+          <t>d1</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Y_T2</t>
+          <t>d2</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Y_T3</t>
+          <t>d3</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Y_T4</t>
+          <t>y1</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Y_T5</t>
+          <t>y2</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>y3</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Y1_T1</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Y2_T1</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Y3_T1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Y1_T2</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Y2_T2</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Y3_T2</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Y1_T3</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Y2_T3</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Y3_T3</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Y1_T4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Y2_T4</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Y3_T4</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Y1_T5</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Y2_T5</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Y3_T5</t>
         </is>
       </c>
     </row>
@@ -473,33 +553,73 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0611</v>
+        <v>0.8622</v>
       </c>
       <c r="C2" t="n">
-        <v>0.286</v>
+        <v>0.7101</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7464</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.4831_x000d_</t>
-        </is>
+        <v>0.6236</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7894</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5030327127145749</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5028256892084659</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4953592384727671</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.500377825440659</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.4916750976459203</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -507,33 +627,73 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5102</v>
+        <v>0.2741</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7464</v>
+        <v>0.1552</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.5965_x000d_</t>
-        </is>
+        <v>0.1333</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1516</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6030036037047214</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6022384010865491</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5988451982026302</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.6027149948272441</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.5980708058276561</v>
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -541,33 +701,73 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0004</v>
+        <v>0.6772</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6916</v>
+        <v>0.8516</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5006</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.5318_x000d_</t>
-        </is>
+        <v>0.6543</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7573</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5433770929582434</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5438184646712733</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5358269320234159</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.5421394198581785</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.5340361622722734</v>
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -575,33 +775,73 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.2178</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4476</v>
+        <v>0.5039</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2648</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.6843_x000d_</t>
-        </is>
+        <v>0.6415</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5039</v>
       </c>
       <c r="F5" t="n">
-        <v>0.712906551111203</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7126173499295344</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.714945114961589</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7134997242883376</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.7132597157920697</v>
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -609,33 +849,73 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1399</v>
+        <v>0.726</v>
       </c>
       <c r="C6" t="n">
-        <v>0.161</v>
+        <v>0.75</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2477</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.2872_x000d_</t>
-        </is>
+        <v>0.7007</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.4953</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2850661706940019</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2868149831761179</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2993259222726771</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.2882238482628415</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.3009865984893266</v>
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -643,33 +923,73 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.6423</v>
+        <v>0.2473</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3229</v>
+        <v>0.2941</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8567</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.7663_x000d_</t>
-        </is>
+        <v>0.4248</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3087</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7603551946850973</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7606804527735812</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7616280688271676</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.762778434736474</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.7615616263311862</v>
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -677,33 +997,73 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6492</v>
+        <v>0.5682</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0007</v>
+        <v>0.5683</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6422</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.5666_x000d_</t>
-        </is>
+        <v>0.5054</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.4426</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5838254415230524</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5812093944792656</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5762973924097419</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.5808837088700072</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.5741624516884267</v>
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -711,33 +1071,73 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1818</v>
+        <v>0.6566</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5078</v>
+        <v>0.6715</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9046</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.6601_x000d_</t>
-        </is>
+        <v>0.4952</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.3951</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6940720613855423</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6949476962980157</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6906551274711515</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.6941248016681848</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.6898749425167816</v>
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -745,33 +1145,73 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7382</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2647</v>
+        <v>0.4717</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1916</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.5427_x000d_</t>
-        </is>
+        <v>0.2921</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.2954</v>
       </c>
       <c r="F10" t="n">
-        <v>0.542941628290569</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5417805273144956</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5383910577796323</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.5408600607854283</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.5383071485468823</v>
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -779,33 +1219,73 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3879</v>
+        <v>0.1187</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1307</v>
+        <v>0.2568</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8656</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.5836_x000d_</t>
-        </is>
+        <v>0.314</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3037</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6203081514928542</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6188105363986017</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6124365020242428</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.6187822217573711</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.6098118392134972</v>
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -813,33 +1293,73 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1903</v>
+        <v>0.5673</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6523</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.782</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.695_x000d_</t>
-        </is>
+        <v>0.4083</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.5552</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7038104037084361</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7046494512078693</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7014656869202005</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.7034497932960893</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.701241759906907</v>
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -847,33 +1367,73 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8401</v>
+        <v>0.3164</v>
       </c>
       <c r="C13" t="n">
-        <v>0.449</v>
+        <v>0.2251</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2719</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.679_x000d_</t>
-        </is>
+        <v>0.3526</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.256</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6825209625950245</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6820747441911876</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6825419912168713</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.6826003711114925</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.6809235027707098</v>
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -881,33 +1441,73 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0029</v>
+        <v>0.7884</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3264</v>
+        <v>0.9568</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2476</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.2956_x000d_</t>
-        </is>
+        <v>0.6825</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6398</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2948504171839176</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2961986401962479</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3089153747037372</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.2992464813110974</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.3078158913858036</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -915,33 +1515,73 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7088</v>
+        <v>0.9633</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9342</v>
+        <v>0.785</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2763</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0.7742_x000d_</t>
-        </is>
+        <v>0.6777</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.6059</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7854854167894719</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7847960687014205</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7888931030446104</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.7856162828516265</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.7893179890932346</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -949,33 +1589,73 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1283</v>
+        <v>0.7739</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1882</v>
+        <v>0.8505</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7252999999999999</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.4662_x000d_</t>
-        </is>
+        <v>0.7934</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6626</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4813133089885561</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4806337442546176</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4744686670552122</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.4782118651507351</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.4708626146033801</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -983,33 +1663,73 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8882</v>
+        <v>0.4219</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3077</v>
+        <v>0.4136</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8931</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0.8093_x000d_</t>
-        </is>
+        <v>0.1408</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.094</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8196747715649869</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8205092729666432</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8238574070762428</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.8232547564927326</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.8250553259076243</v>
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1017,33 +1737,73 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.2225</v>
+        <v>0.6616</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9182</v>
+        <v>0.4365</v>
       </c>
       <c r="D18" t="n">
-        <v>0.782</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.7581_x000d_</t>
-        </is>
+        <v>0.6597</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8129</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7852775309551429</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7851446215017266</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7880681434828505</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.7847751255361289</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.7893716444561825</v>
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1051,101 +1811,193 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1957</v>
+        <v>0.7325</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8423</v>
+        <v>0.4761</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3085</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0.5826_x000d_</t>
-        </is>
+        <v>0.3888</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5683</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6049686651574635</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6043653521565573</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5986933336558092</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.6038786626312181</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.5982572057127205</v>
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
-        <v>0.9991</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.5914</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.3933</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0.7938_x000d_</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0.7993815985466709</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.8002157667501946</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.8052280060382204</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.8009611706514791</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.8044642895557923</v>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
-        <v>0.2299</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.1524</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.7353</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0.5012</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0.5131497170173004</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.5120457156578962</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.5052067217799943</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.5098142166616999</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.5018402301633857</v>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/validacao.xlsx
+++ b/datasets/validacao.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,90 +459,75 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>y1</t>
+          <t>Y1_T1</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>y2</t>
+          <t>Y2_T1</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>y3</t>
+          <t>Y3_T1</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Y1_T1</t>
+          <t>Y1_T2</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Y2_T1</t>
+          <t>Y2_T2</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Y3_T1</t>
+          <t>Y3_T2</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Y1_T2</t>
+          <t>Y1_T3</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Y2_T2</t>
+          <t>Y2_T3</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Y3_T2</t>
+          <t>Y3_T3</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Y1_T3</t>
+          <t>Y1_T4</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Y2_T3</t>
+          <t>Y2_T4</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Y3_T3</t>
+          <t>Y3_T4</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Y1_T4</t>
+          <t>Y1_T5</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Y2_T4</t>
+          <t>Y2_T5</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
-        <is>
-          <t>Y3_T4</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Y1_T5</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Y2_T5</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
         <is>
           <t>Y3_T5</t>
         </is>
@@ -573,9 +558,15 @@
       <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
@@ -610,15 +601,6 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -647,9 +629,15 @@
       <c r="H3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
@@ -684,15 +672,6 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -721,9 +700,15 @@
       <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -758,15 +743,6 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -795,9 +771,15 @@
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
@@ -832,15 +814,6 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -869,9 +842,15 @@
       <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
@@ -906,15 +885,6 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -943,9 +913,15 @@
       <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
@@ -980,15 +956,6 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1017,9 +984,15 @@
       <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
@@ -1054,15 +1027,6 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1091,9 +1055,15 @@
       <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
@@ -1128,15 +1098,6 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1165,9 +1126,15 @@
       <c r="H10" t="n">
         <v>0</v>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
@@ -1202,15 +1169,6 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1239,9 +1197,15 @@
       <c r="H11" t="n">
         <v>0</v>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
@@ -1276,15 +1240,6 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1313,9 +1268,15 @@
       <c r="H12" t="n">
         <v>0</v>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
@@ -1350,15 +1311,6 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1387,9 +1339,15 @@
       <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
       <c r="L13" t="n">
         <v>1</v>
       </c>
@@ -1424,15 +1382,6 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1461,9 +1410,15 @@
       <c r="H14" t="n">
         <v>1</v>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
@@ -1498,15 +1453,6 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1535,9 +1481,15 @@
       <c r="H15" t="n">
         <v>1</v>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
@@ -1572,15 +1524,6 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1609,9 +1552,15 @@
       <c r="H16" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
@@ -1646,15 +1595,6 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1683,9 +1623,15 @@
       <c r="H17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
       <c r="L17" t="n">
         <v>1</v>
       </c>
@@ -1720,15 +1666,6 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1757,9 +1694,15 @@
       <c r="H18" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
@@ -1794,15 +1737,6 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1831,9 +1765,15 @@
       <c r="H19" t="n">
         <v>0</v>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
@@ -1868,135 +1808,6 @@
         <v>1</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/datasets/validacao.xlsx
+++ b/datasets/validacao.xlsx
@@ -485,19 +485,19 @@
         <v>0.4831</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.487</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4965</v>
+        <v>0.4894</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4862</v>
+        <v>0.4895</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.4942</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4895</v>
+        <v>0.4911</v>
       </c>
     </row>
     <row r="3">
@@ -517,19 +517,19 @@
         <v>0.5965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6024</v>
+        <v>0.5949</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6009</v>
+        <v>0.5964</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5966</v>
+        <v>0.5975</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6058</v>
+        <v>0.5916</v>
       </c>
       <c r="J3" t="n">
-        <v>0.594</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="4">
@@ -549,19 +549,19 @@
         <v>0.5318000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5407</v>
+        <v>0.5294</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5356</v>
+        <v>0.5311</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5296</v>
+        <v>0.5313</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5425</v>
+        <v>0.53</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5338000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -581,19 +581,19 @@
         <v>0.6843</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7091</v>
+        <v>0.7048</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7115</v>
+        <v>0.7085</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7096</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7129</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7057</v>
+        <v>0.6952</v>
       </c>
     </row>
     <row r="6">
@@ -613,19 +613,19 @@
         <v>0.2872</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3032</v>
+        <v>0.2845</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2901</v>
+        <v>0.2874</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2836</v>
+        <v>0.279</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3069</v>
+        <v>0.3012</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2919</v>
+        <v>0.3068</v>
       </c>
     </row>
     <row r="7">
@@ -645,19 +645,19 @@
         <v>0.7663</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7548</v>
+        <v>0.7501</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7538</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7561</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.7416</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7504999999999999</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="8">
@@ -677,19 +677,19 @@
         <v>0.5666</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5814</v>
+        <v>0.5712</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5815</v>
+        <v>0.5736</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5733</v>
+        <v>0.5755</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5821</v>
+        <v>0.5777</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5735</v>
+        <v>0.5659</v>
       </c>
     </row>
     <row r="9">
@@ -709,19 +709,19 @@
         <v>0.6601</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6848</v>
+        <v>0.6791</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6865</v>
+        <v>0.6829</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6838</v>
+        <v>0.6842</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6898</v>
+        <v>0.6742</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6803</v>
+        <v>0.6644</v>
       </c>
     </row>
     <row r="10">
@@ -741,19 +741,19 @@
         <v>0.5427</v>
       </c>
       <c r="F10" t="n">
-        <v>0.544</v>
+        <v>0.5359</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5447</v>
+        <v>0.5369</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5373</v>
+        <v>0.5369</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5411</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5366</v>
+        <v>0.5424</v>
       </c>
     </row>
     <row r="11">
@@ -773,19 +773,19 @@
         <v>0.5836</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6145</v>
+        <v>0.6042</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6145</v>
+        <v>0.6076</v>
       </c>
       <c r="H11" t="n">
+        <v>0.6099</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.6073</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.6169</v>
-      </c>
       <c r="J11" t="n">
-        <v>0.6069</v>
+        <v>0.5945</v>
       </c>
     </row>
     <row r="12">
@@ -805,19 +805,19 @@
         <v>0.695</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6953</v>
+        <v>0.6905</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6964</v>
+        <v>0.6939</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6946</v>
+        <v>0.6949</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6998</v>
+        <v>0.6836</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6906</v>
+        <v>0.6758999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -837,19 +837,19 @@
         <v>0.679</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6794</v>
+        <v>0.6741</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6813</v>
+        <v>0.6772</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6781</v>
+        <v>0.6798</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6693</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6747</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="14">
@@ -869,19 +869,19 @@
         <v>0.2956</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3124</v>
+        <v>0.2929</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2986</v>
+        <v>0.2951</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2916</v>
+        <v>0.2894</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3144</v>
+        <v>0.3087</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3015</v>
+        <v>0.316</v>
       </c>
     </row>
     <row r="15">
@@ -901,19 +901,19 @@
         <v>0.7742</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7796</v>
+        <v>0.7774</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7821</v>
+        <v>0.7804</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7824</v>
+        <v>0.784</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7837</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7763</v>
+        <v>0.7594</v>
       </c>
     </row>
     <row r="16">
@@ -933,19 +933,19 @@
         <v>0.4662</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4803</v>
+        <v>0.4664</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4762</v>
+        <v>0.4686</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4652</v>
+        <v>0.4682</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4835</v>
+        <v>0.4756</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4689</v>
+        <v>0.472</v>
       </c>
     </row>
     <row r="17">
@@ -965,19 +965,19 @@
         <v>0.8093</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8145</v>
+        <v>0.8123</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8147</v>
+        <v>0.8159</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8191000000000001</v>
+        <v>0.8203</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8151</v>
+        <v>0.7992</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.7897</v>
       </c>
     </row>
     <row r="18">
@@ -997,19 +997,19 @@
         <v>0.7581</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.7759</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7789</v>
+        <v>0.7783</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7804</v>
+        <v>0.78</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7803</v>
+        <v>0.7642</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7739</v>
+        <v>0.7537</v>
       </c>
     </row>
     <row r="19">
@@ -1029,19 +1029,19 @@
         <v>0.5826</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6022</v>
+        <v>0.5937</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5985</v>
+        <v>0.5955</v>
       </c>
       <c r="H19" t="n">
-        <v>0.595</v>
+        <v>0.596</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6044</v>
+        <v>0.5894</v>
       </c>
       <c r="J19" t="n">
-        <v>0.593</v>
+        <v>0.5935</v>
       </c>
     </row>
     <row r="20">
@@ -1061,19 +1061,19 @@
         <v>0.7938</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7935</v>
+        <v>0.7916</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7963</v>
+        <v>0.7957</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.7993</v>
       </c>
       <c r="I20" t="n">
-        <v>0.797</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7919</v>
+        <v>0.7747000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1093,16 +1093,16 @@
         <v>0.5012</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5107</v>
+        <v>0.4978</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5082</v>
+        <v>0.5002</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4976</v>
+        <v>0.5004</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5137</v>
+        <v>0.5062</v>
       </c>
       <c r="J21" t="n">
         <v>0.5003</v>
